--- a/public/upload/to_import_gmao_nextjs.xlsx
+++ b/public/upload/to_import_gmao_nextjs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12192" windowHeight="7488" tabRatio="891" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12192" windowHeight="7488" tabRatio="891" firstSheet="7" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="sites" sheetId="1" r:id="rId1"/>
@@ -16,20 +16,21 @@
     <sheet name="pannes" sheetId="15" r:id="rId7"/>
     <sheet name="saisie_hrm" sheetId="27" r:id="rId8"/>
     <sheet name="saisie_hims" sheetId="28" r:id="rId9"/>
-    <sheet name="permissions" sheetId="29" r:id="rId10"/>
-    <sheet name="roles" sheetId="30" r:id="rId11"/>
-    <sheet name="type_organe" sheetId="31" r:id="rId12"/>
-    <sheet name="organe" sheetId="32" r:id="rId13"/>
-    <sheet name="mvt_organeTest" sheetId="33" r:id="rId14"/>
-    <sheet name="mvt_organe" sheetId="34" r:id="rId15"/>
+    <sheet name="objectifs" sheetId="35" r:id="rId10"/>
+    <sheet name="permissions" sheetId="29" r:id="rId11"/>
+    <sheet name="roles" sheetId="30" r:id="rId12"/>
+    <sheet name="type_organe" sheetId="31" r:id="rId13"/>
+    <sheet name="organe" sheetId="32" r:id="rId14"/>
+    <sheet name="mvt_organeTest" sheetId="33" r:id="rId15"/>
+    <sheet name="mvt_organe" sheetId="34" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">backlogs!$A$1:$K$412</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">engins!$A$1:$E$250</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">mvt_organe!$A$1:$G$268</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">mvt_organe!$A$1:$G$268</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">pannes!$A$1:$E$786</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">permissions!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">roles!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">permissions!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">roles!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">saisie_hims!$A$1:$F$601</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">saisie_hrm!$A$1:$E$601</definedName>
   </definedNames>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13013" uniqueCount="1722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13056" uniqueCount="1729">
   <si>
     <t>name</t>
   </si>
@@ -5240,6 +5241,27 @@
   </si>
   <si>
     <t>31/06/2026</t>
+  </si>
+  <si>
+    <t>dispo</t>
+  </si>
+  <si>
+    <t>mtbf</t>
+  </si>
+  <si>
+    <t>tdm</t>
+  </si>
+  <si>
+    <t>spe_huile</t>
+  </si>
+  <si>
+    <t>spe_go</t>
+  </si>
+  <si>
+    <t>spe_graisse</t>
+  </si>
+  <si>
+    <t>annee</t>
   </si>
 </sst>
 </file>
@@ -5363,7 +5385,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5477,6 +5499,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Neutre 2" xfId="2"/>
@@ -5813,6 +5841,545 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="43"/>
+    <col min="2" max="3" width="11.5546875" style="1"/>
+    <col min="4" max="9" width="11.5546875" style="44"/>
+    <col min="10" max="16384" width="11.5546875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="43" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>1724</v>
+      </c>
+      <c r="G1" s="44" t="s">
+        <v>1725</v>
+      </c>
+      <c r="H1" s="44" t="s">
+        <v>1726</v>
+      </c>
+      <c r="I1" s="44" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="43">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="44">
+        <v>85</v>
+      </c>
+      <c r="E2" s="44">
+        <v>20</v>
+      </c>
+      <c r="F2" s="44">
+        <v>77</v>
+      </c>
+      <c r="G2" s="44">
+        <v>16</v>
+      </c>
+      <c r="H2" s="44">
+        <v>99</v>
+      </c>
+      <c r="I2" s="44">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="43">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="44">
+        <v>82</v>
+      </c>
+      <c r="E3" s="44">
+        <v>18</v>
+      </c>
+      <c r="F3" s="44">
+        <v>72</v>
+      </c>
+      <c r="G3" s="44">
+        <v>12</v>
+      </c>
+      <c r="H3" s="44">
+        <v>77.5</v>
+      </c>
+      <c r="I3" s="44">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="43">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="44">
+        <v>85</v>
+      </c>
+      <c r="E4" s="44">
+        <v>20</v>
+      </c>
+      <c r="F4" s="44">
+        <v>80</v>
+      </c>
+      <c r="G4" s="44">
+        <v>16</v>
+      </c>
+      <c r="H4" s="44">
+        <v>99</v>
+      </c>
+      <c r="I4" s="44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="43">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="44">
+        <v>82</v>
+      </c>
+      <c r="E5" s="44">
+        <v>18</v>
+      </c>
+      <c r="F5" s="44">
+        <v>77</v>
+      </c>
+      <c r="G5" s="44">
+        <v>12</v>
+      </c>
+      <c r="H5" s="44">
+        <v>88</v>
+      </c>
+      <c r="I5" s="44">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="43">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="44">
+        <v>85</v>
+      </c>
+      <c r="E6" s="44">
+        <v>19</v>
+      </c>
+      <c r="F6" s="44">
+        <v>77</v>
+      </c>
+      <c r="G6" s="44">
+        <v>9.9</v>
+      </c>
+      <c r="H6" s="44">
+        <v>99</v>
+      </c>
+      <c r="I6" s="44">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="43">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="44">
+        <v>89</v>
+      </c>
+      <c r="E7" s="44">
+        <v>20</v>
+      </c>
+      <c r="F7" s="44">
+        <v>80</v>
+      </c>
+      <c r="G7" s="44">
+        <v>16</v>
+      </c>
+      <c r="H7" s="44">
+        <v>88</v>
+      </c>
+      <c r="I7" s="44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="43">
+        <v>2026</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="44">
+        <v>85</v>
+      </c>
+      <c r="E8" s="44">
+        <v>18</v>
+      </c>
+      <c r="F8" s="44">
+        <v>80</v>
+      </c>
+      <c r="G8" s="44">
+        <v>12</v>
+      </c>
+      <c r="H8" s="44">
+        <v>99</v>
+      </c>
+      <c r="I8" s="44">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="43">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="44">
+        <v>82</v>
+      </c>
+      <c r="E9" s="44">
+        <v>18</v>
+      </c>
+      <c r="F9" s="44">
+        <v>77</v>
+      </c>
+      <c r="G9" s="44">
+        <v>9.9</v>
+      </c>
+      <c r="H9" s="44">
+        <v>88</v>
+      </c>
+      <c r="I9" s="44">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="43">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="44">
+        <v>85</v>
+      </c>
+      <c r="E10" s="44">
+        <v>19</v>
+      </c>
+      <c r="F10" s="44">
+        <v>72</v>
+      </c>
+      <c r="G10" s="44">
+        <v>12</v>
+      </c>
+      <c r="H10" s="44">
+        <v>99</v>
+      </c>
+      <c r="I10" s="44">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="43">
+        <v>2026</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="44">
+        <v>85</v>
+      </c>
+      <c r="E11" s="44">
+        <v>18</v>
+      </c>
+      <c r="F11" s="44">
+        <v>80</v>
+      </c>
+      <c r="G11" s="44">
+        <v>16</v>
+      </c>
+      <c r="H11" s="44">
+        <v>88</v>
+      </c>
+      <c r="I11" s="44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="43">
+        <v>2026</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="44">
+        <v>82</v>
+      </c>
+      <c r="E12" s="44">
+        <v>20</v>
+      </c>
+      <c r="F12" s="44">
+        <v>72</v>
+      </c>
+      <c r="G12" s="44">
+        <v>12</v>
+      </c>
+      <c r="H12" s="44">
+        <v>77.5</v>
+      </c>
+      <c r="I12" s="44">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="43">
+        <v>2026</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="44">
+        <v>85</v>
+      </c>
+      <c r="E13" s="44">
+        <v>18</v>
+      </c>
+      <c r="F13" s="44">
+        <v>80</v>
+      </c>
+      <c r="G13" s="44">
+        <v>9.9</v>
+      </c>
+      <c r="H13" s="44">
+        <v>88</v>
+      </c>
+      <c r="I13" s="44">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="43">
+        <v>2026</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="44">
+        <v>89</v>
+      </c>
+      <c r="E14" s="44">
+        <v>19</v>
+      </c>
+      <c r="F14" s="44">
+        <v>77</v>
+      </c>
+      <c r="G14" s="44">
+        <v>12</v>
+      </c>
+      <c r="H14" s="44">
+        <v>99</v>
+      </c>
+      <c r="I14" s="44">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="43">
+        <v>2026</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="44">
+        <v>85</v>
+      </c>
+      <c r="E15" s="44">
+        <v>18</v>
+      </c>
+      <c r="F15" s="44">
+        <v>80</v>
+      </c>
+      <c r="G15" s="44">
+        <v>16</v>
+      </c>
+      <c r="H15" s="44">
+        <v>88</v>
+      </c>
+      <c r="I15" s="44">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="43">
+        <v>2026</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="44">
+        <v>89</v>
+      </c>
+      <c r="E16" s="44">
+        <v>20</v>
+      </c>
+      <c r="F16" s="44">
+        <v>72</v>
+      </c>
+      <c r="G16" s="44">
+        <v>12</v>
+      </c>
+      <c r="H16" s="44">
+        <v>77.5</v>
+      </c>
+      <c r="I16" s="44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="43">
+        <v>2026</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="44">
+        <v>82</v>
+      </c>
+      <c r="E17" s="44">
+        <v>18</v>
+      </c>
+      <c r="F17" s="44">
+        <v>77</v>
+      </c>
+      <c r="G17" s="44">
+        <v>16</v>
+      </c>
+      <c r="H17" s="44">
+        <v>88</v>
+      </c>
+      <c r="I17" s="44">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="43">
+        <v>2026</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="44">
+        <v>89</v>
+      </c>
+      <c r="E18" s="44">
+        <v>19</v>
+      </c>
+      <c r="F18" s="44">
+        <v>80</v>
+      </c>
+      <c r="G18" s="44">
+        <v>12</v>
+      </c>
+      <c r="H18" s="44">
+        <v>99</v>
+      </c>
+      <c r="I18" s="44">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6004,7 +6571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6075,7 +6642,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6177,7 +6744,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I268"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8374,7 +8941,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8595,7 +9162,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G535"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
